--- a/Encollect_Web_DBS_P1/Cypress/fixtures/AllocationToOwner.xlsx
+++ b/Encollect_Web_DBS_P1/Cypress/fixtures/AllocationToOwner.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0DED628-23FE-4885-92DD-181DCE8B92C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40887E5E-964A-4D5A-979E-AE877AA2343C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,8 +22,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -42,13 +40,13 @@
     <t>AllocationOwnerCode</t>
   </si>
   <si>
-    <t>2025-10-10</t>
-  </si>
-  <si>
-    <t>5937</t>
-  </si>
-  <si>
-    <t>68210000012749</t>
+    <t>2027-10-10</t>
+  </si>
+  <si>
+    <t>0210773000022710</t>
+  </si>
+  <si>
+    <t>1161</t>
   </si>
 </sst>
 </file>
@@ -368,15 +366,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.77734375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.88671875" style="1"/>
+    <col min="4" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -387,12 +385,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>3</v>

--- a/Encollect_Web_DBS_P1/Cypress/fixtures/AllocationToOwner.xlsx
+++ b/Encollect_Web_DBS_P1/Cypress/fixtures/AllocationToOwner.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40887E5E-964A-4D5A-979E-AE877AA2343C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0DED628-23FE-4885-92DD-181DCE8B92C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -40,13 +42,13 @@
     <t>AllocationOwnerCode</t>
   </si>
   <si>
-    <t>2027-10-10</t>
-  </si>
-  <si>
-    <t>0210773000022710</t>
-  </si>
-  <si>
-    <t>1161</t>
+    <t>2025-10-10</t>
+  </si>
+  <si>
+    <t>5937</t>
+  </si>
+  <si>
+    <t>68210000012749</t>
   </si>
 </sst>
 </file>
@@ -366,15 +368,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.77734375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.85546875" style="1"/>
+    <col min="4" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -385,12 +387,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>5</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>3</v>
